--- a/tests/ITER_2D_APEC_evol_fine2/input_template.xlsx
+++ b/tests/ITER_2D_APEC_evol_fine2/input_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="element_types"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="50">
   <si>
     <t>SETTING</t>
   </si>
@@ -29,7 +29,7 @@
     <t>ksp_type</t>
   </si>
   <si>
-    <t>kspreonly</t>
+    <t>preonly</t>
   </si>
   <si>
     <t>pc_type</t>
@@ -45,87 +45,6 @@
   </si>
   <si>
     <t>minimum_linear_tolerance</t>
-  </si>
-  <si>
-    <t>linear_tolerance_multiplier</t>
-  </si>
-  <si>
-    <t>write_full_matrix</t>
-  </si>
-  <si>
-    <t>timesolver_tolerance</t>
-  </si>
-  <si>
-    <t>analytic_jacobians</t>
-  </si>
-  <si>
-    <t>verify_analytic_jacobians</t>
-  </si>
-  <si>
-    <t>numerical_jacobian_h</t>
-  </si>
-  <si>
-    <t>quiet</t>
-  </si>
-  <si>
-    <t>max_nonlinear_it</t>
-  </si>
-  <si>
-    <t>min_steplength</t>
-  </si>
-  <si>
-    <t>relative_step_tolerance</t>
-  </si>
-  <si>
-    <t>require_residual_reduction</t>
-  </si>
-  <si>
-    <t>reduce_deltat_on_diffsolver_failure</t>
-  </si>
-  <si>
-    <t>continue_after_max_iterations</t>
-  </si>
-  <si>
-    <t>continue_after_backtrack_failure</t>
-  </si>
-  <si>
-    <t>timesolver_core</t>
-  </si>
-  <si>
-    <t>print_solution_norms</t>
-  </si>
-  <si>
-    <t>print_solutions</t>
-  </si>
-  <si>
-    <t>print_residual_norms</t>
-  </si>
-  <si>
-    <t>print_residuals</t>
-  </si>
-  <si>
-    <t>print_jacobian_norms</t>
-  </si>
-  <si>
-    <t>print_jacobians</t>
-  </si>
-  <si>
-    <t>print_element_solutions</t>
-  </si>
-  <si>
-    <t>print_element_residuals</t>
-  </si>
-  <si>
-    <t>print_element_jacobians</t>
-  </si>
-  <si>
-    <t>constrain_in_solver</t>
-  </si>
-  <si>
-    <t>use_petsc_snes</t>
-  </si>
-  <si>
-    <t>min_step_length</t>
   </si>
   <si>
     <t>CONSTANTS_ID</t>
@@ -258,7 +177,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,12 +188,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -306,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -327,9 +240,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -648,25 +558,25 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>71</v>
+        <v>43</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
@@ -780,10 +690,10 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
@@ -791,7 +701,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
@@ -799,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
@@ -807,7 +717,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
@@ -815,7 +725,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
@@ -823,7 +733,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
@@ -831,7 +741,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
@@ -839,7 +749,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
@@ -847,7 +757,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
@@ -855,7 +765,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
@@ -863,7 +773,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
@@ -871,7 +781,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
@@ -879,7 +789,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
@@ -887,7 +797,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
@@ -895,7 +805,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
@@ -903,7 +813,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
@@ -911,7 +821,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
@@ -919,7 +829,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
@@ -927,7 +837,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
@@ -935,7 +845,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
@@ -943,7 +853,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
@@ -951,7 +861,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
@@ -959,7 +869,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
@@ -967,7 +877,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
@@ -975,7 +885,7 @@
         <v>16</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1005,34 +915,34 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="3" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
@@ -1200,64 +1110,64 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="3" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
@@ -2138,7 +2048,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="4" width="34.005" customWidth="1" bestFit="1"/>
@@ -2193,222 +2103,6 @@
         <v>1e-10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="3">
-        <v>25</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2">
-        <v>0.000001</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="2">
-        <v>0.000001</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
